--- a/product-definitions/spreadsheet/iwv-lwp.xlsx
+++ b/product-definitions/spreadsheet/iwv-lwp.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -310,14 +310,9 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -335,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -350,17 +345,16 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -369,10 +363,10 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -1674,7 +1668,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -1682,23 +1676,23 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -1706,60 +1700,60 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="5" t="s">
@@ -1767,7 +1761,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="5" t="s">
@@ -1775,1521 +1769,1522 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="6">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="6" t="s">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="B21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="6" t="s">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="B22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="6" t="s">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="B23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="6" t="s">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="B24" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="9" t="s">
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10" t="s">
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10" t="s">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10" t="s">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10" t="s">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="10"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10" t="s">
+      <c r="C30" s="9"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10" t="s">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="10"/>
-      <c r="B33" s="13" t="s">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="9"/>
+      <c r="B33" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="s">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10" t="s">
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10" t="s">
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10" t="s">
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="9"/>
+      <c r="B38" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10" t="s">
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="9"/>
+      <c r="B39" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="10"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10" t="s">
+      <c r="C39" s="9"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10" t="s">
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="10"/>
-      <c r="B42" s="13" t="s">
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="9"/>
+      <c r="B42" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="10"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="9" t="s">
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10"/>
-      <c r="B45" s="10" t="s">
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10" t="s">
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="9"/>
+      <c r="B46" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="10"/>
-      <c r="B47" s="10" t="s">
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="9"/>
+      <c r="B47" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="10"/>
-      <c r="B48" s="10" t="s">
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="9"/>
+      <c r="B48" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C48" s="10"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="10"/>
-      <c r="B49" s="10" t="s">
+      <c r="C48" s="9"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="9"/>
+      <c r="B49" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="10"/>
-      <c r="B50" s="10" t="s">
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="9"/>
+      <c r="B50" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="10"/>
-      <c r="B51" s="13" t="s">
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="9"/>
+      <c r="B51" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C51" s="14" t="s">
+      <c r="C51" s="13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="10"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="s">
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="9"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="10"/>
-      <c r="B54" s="10" t="s">
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="9"/>
+      <c r="B54" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="10"/>
-      <c r="B55" s="10" t="s">
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="9"/>
+      <c r="B55" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="10"/>
-      <c r="B56" s="10" t="s">
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="9"/>
+      <c r="B56" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C56" s="11">
+      <c r="C56" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="10"/>
-      <c r="B57" s="10" t="s">
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="9"/>
+      <c r="B57" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C57" s="10"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10"/>
-      <c r="B58" s="10" t="s">
+      <c r="C57" s="9"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="9"/>
+      <c r="B58" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C58" s="9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="10"/>
-      <c r="B59" s="10" t="s">
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="9"/>
+      <c r="B59" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="10"/>
-      <c r="B60" s="13" t="s">
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="9"/>
+      <c r="B60" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="10"/>
-      <c r="B61" s="10"/>
-      <c r="C61" s="10"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="9" t="s">
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="9"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B62" s="10"/>
-      <c r="C62" s="10"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="10"/>
-      <c r="B63" s="10" t="s">
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="9"/>
+      <c r="B63" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="10" t="s">
+      <c r="C63" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="10"/>
-      <c r="B64" s="10" t="s">
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="9"/>
+      <c r="B64" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C64" s="10" t="s">
+      <c r="C64" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="10"/>
-      <c r="B65" s="10" t="s">
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="9"/>
+      <c r="B65" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C65" s="11">
+      <c r="C65" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="10"/>
-      <c r="B66" s="10" t="s">
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="9"/>
+      <c r="B66" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="10"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10"/>
-      <c r="B67" s="10" t="s">
+      <c r="C66" s="9"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="9"/>
+      <c r="B67" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="C67" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="10"/>
-      <c r="B68" s="10" t="s">
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="9"/>
+      <c r="B68" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="10"/>
-      <c r="B69" s="13" t="s">
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="9"/>
+      <c r="B69" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C69" s="14" t="s">
+      <c r="C69" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="10"/>
-      <c r="B70" s="10"/>
-      <c r="C70" s="10"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="9" t="s">
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="9"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B71" s="10"/>
-      <c r="C71" s="10"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="10"/>
-      <c r="B72" s="10" t="s">
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="9"/>
+      <c r="B72" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C72" s="10" t="s">
+      <c r="C72" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="10"/>
-      <c r="B73" s="10" t="s">
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="9"/>
+      <c r="B73" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C73" s="10" t="s">
+      <c r="C73" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="10"/>
-      <c r="B74" s="10" t="s">
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="9"/>
+      <c r="B74" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C74" s="11">
+      <c r="C74" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="10"/>
-      <c r="B75" s="10" t="s">
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="9"/>
+      <c r="B75" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C75" s="10"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="10"/>
-      <c r="B76" s="10" t="s">
+      <c r="C75" s="9"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="9"/>
+      <c r="B76" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="10"/>
-      <c r="B77" s="10" t="s">
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="9"/>
+      <c r="B77" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="10"/>
-      <c r="B78" s="13" t="s">
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="9"/>
+      <c r="B78" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="10"/>
-      <c r="B79" s="10"/>
-      <c r="C79" s="10"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="9" t="s">
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="9"/>
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B80" s="10"/>
-      <c r="C80" s="10"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="10"/>
-      <c r="B81" s="10" t="s">
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="9"/>
+      <c r="B81" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C81" s="10" t="s">
+      <c r="C81" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="10"/>
-      <c r="B82" s="10" t="s">
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="9"/>
+      <c r="B82" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C82" s="10" t="s">
+      <c r="C82" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="10"/>
-      <c r="B83" s="10" t="s">
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="9"/>
+      <c r="B83" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C83" s="11">
+      <c r="C83" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="10"/>
-      <c r="B84" s="10" t="s">
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="9"/>
+      <c r="B84" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C84" s="10"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="10"/>
-      <c r="B85" s="10" t="s">
+      <c r="C84" s="9"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="9"/>
+      <c r="B85" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C85" s="9" t="s">
+      <c r="C85" s="8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="10"/>
-      <c r="B86" s="10" t="s">
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="9"/>
+      <c r="B86" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C86" s="12" t="s">
+      <c r="C86" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="10"/>
-      <c r="B87" s="13" t="s">
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="9"/>
+      <c r="B87" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C87" s="14" t="s">
+      <c r="C87" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="10"/>
-      <c r="B88" s="10"/>
-      <c r="C88" s="10"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="9" t="s">
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="9"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="9"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B89" s="10"/>
-      <c r="C89" s="10"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="10"/>
-      <c r="B90" s="10" t="s">
+      <c r="B89" s="9"/>
+      <c r="C89" s="9"/>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="9"/>
+      <c r="B90" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C90" s="10" t="s">
+      <c r="C90" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="10"/>
-      <c r="B91" s="10" t="s">
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="9"/>
+      <c r="B91" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C91" s="10" t="s">
+      <c r="C91" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="10"/>
-      <c r="B92" s="10" t="s">
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="9"/>
+      <c r="B92" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C92" s="11">
+      <c r="C92" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="10"/>
-      <c r="B93" s="10" t="s">
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="9"/>
+      <c r="B93" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C93" s="10"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="10"/>
-      <c r="B94" s="10" t="s">
+      <c r="C93" s="9"/>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="9"/>
+      <c r="B94" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C94" s="9" t="s">
+      <c r="C94" s="8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="10"/>
-      <c r="B95" s="10" t="s">
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="9"/>
+      <c r="B95" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C95" s="12" t="s">
+      <c r="C95" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="10"/>
-      <c r="B96" s="13" t="s">
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="9"/>
+      <c r="B96" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C96" s="14" t="s">
+      <c r="C96" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="10"/>
-      <c r="B97" s="10"/>
-      <c r="C97" s="10"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="9" t="s">
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="9"/>
+      <c r="B97" s="9"/>
+      <c r="C97" s="9"/>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B98" s="10"/>
-      <c r="C98" s="10"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="10"/>
-      <c r="B99" s="10" t="s">
+      <c r="B98" s="9"/>
+      <c r="C98" s="9"/>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="9"/>
+      <c r="B99" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C99" s="10" t="s">
+      <c r="C99" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="10"/>
-      <c r="B100" s="10" t="s">
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="9"/>
+      <c r="B100" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C100" s="10" t="s">
+      <c r="C100" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="10"/>
-      <c r="B101" s="10" t="s">
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="9"/>
+      <c r="B101" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C101" s="11">
+      <c r="C101" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="10"/>
-      <c r="B102" s="10" t="s">
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="9"/>
+      <c r="B102" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C102" s="10"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="10"/>
-      <c r="B103" s="10" t="s">
+      <c r="C102" s="9"/>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="9"/>
+      <c r="B103" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C103" s="9" t="s">
+      <c r="C103" s="8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="10"/>
-      <c r="B104" s="10" t="s">
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="9"/>
+      <c r="B104" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C104" s="12" t="s">
+      <c r="C104" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="10"/>
-      <c r="B105" s="13" t="s">
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="9"/>
+      <c r="B105" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C105" s="14" t="s">
+      <c r="C105" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="10"/>
-      <c r="B106" s="10"/>
-      <c r="C106" s="10"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="9" t="s">
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="9"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="9"/>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B107" s="10"/>
-      <c r="C107" s="10"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="10"/>
-      <c r="B108" s="10" t="s">
+      <c r="B107" s="9"/>
+      <c r="C107" s="9"/>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="A108" s="9"/>
+      <c r="B108" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C108" s="10" t="s">
+      <c r="C108" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="10"/>
-      <c r="B109" s="10" t="s">
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="9"/>
+      <c r="B109" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C109" s="10" t="s">
+      <c r="C109" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="10"/>
-      <c r="B110" s="10" t="s">
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="9"/>
+      <c r="B110" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C110" s="11">
+      <c r="C110" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="10"/>
-      <c r="B111" s="10" t="s">
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="9"/>
+      <c r="B111" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C111" s="10"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="10"/>
-      <c r="B112" s="10" t="s">
+      <c r="C111" s="9"/>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="9"/>
+      <c r="B112" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C112" s="9" t="s">
+      <c r="C112" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="10"/>
-      <c r="B113" s="10" t="s">
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="9"/>
+      <c r="B113" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C113" s="12" t="s">
+      <c r="C113" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="10"/>
-      <c r="B114" s="13" t="s">
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="9"/>
+      <c r="B114" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C114" s="14" t="s">
+      <c r="C114" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="10"/>
-      <c r="B115" s="10"/>
-      <c r="C115" s="10"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="9" t="s">
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="9"/>
+      <c r="B115" s="9"/>
+      <c r="C115" s="9"/>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B116" s="10"/>
-      <c r="C116" s="10"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="10"/>
-      <c r="B117" s="10" t="s">
+      <c r="B116" s="9"/>
+      <c r="C116" s="9"/>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="9"/>
+      <c r="B117" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C117" s="10" t="s">
+      <c r="C117" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="10"/>
-      <c r="B118" s="10" t="s">
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="9"/>
+      <c r="B118" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C118" s="10" t="s">
+      <c r="C118" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="10"/>
-      <c r="B119" s="10" t="s">
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="9"/>
+      <c r="B119" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C119" s="11">
+      <c r="C119" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="10"/>
-      <c r="B120" s="10" t="s">
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="9"/>
+      <c r="B120" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C120" s="10"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="10"/>
-      <c r="B121" s="10" t="s">
+      <c r="C120" s="9"/>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="9"/>
+      <c r="B121" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C121" s="9" t="s">
+      <c r="C121" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="10"/>
-      <c r="B122" s="10" t="s">
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="9"/>
+      <c r="B122" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C122" s="12" t="s">
+      <c r="C122" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="10"/>
-      <c r="B123" s="13" t="s">
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="9"/>
+      <c r="B123" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C123" s="14" t="s">
+      <c r="C123" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="10"/>
-      <c r="B124" s="10"/>
-      <c r="C124" s="10"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="9" t="s">
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="A124" s="9"/>
+      <c r="B124" s="9"/>
+      <c r="C124" s="9"/>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="A125" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B125" s="10"/>
-      <c r="C125" s="10"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="10"/>
-      <c r="B126" s="10" t="s">
+      <c r="B125" s="9"/>
+      <c r="C125" s="9"/>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="9"/>
+      <c r="B126" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C126" s="10" t="s">
+      <c r="C126" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="10"/>
-      <c r="B127" s="10" t="s">
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="A127" s="9"/>
+      <c r="B127" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C127" s="10" t="s">
+      <c r="C127" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="10"/>
-      <c r="B128" s="10" t="s">
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="A128" s="9"/>
+      <c r="B128" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C128" s="11">
+      <c r="C128" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="10"/>
-      <c r="B129" s="10" t="s">
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="A129" s="9"/>
+      <c r="B129" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C129" s="10"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="10"/>
-      <c r="B130" s="10" t="s">
+      <c r="C129" s="9"/>
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="A130" s="9"/>
+      <c r="B130" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C130" s="9" t="s">
+      <c r="C130" s="8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="10"/>
-      <c r="B131" s="10" t="s">
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="A131" s="9"/>
+      <c r="B131" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C131" s="12" t="s">
+      <c r="C131" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="10"/>
-      <c r="B132" s="13" t="s">
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="A132" s="9"/>
+      <c r="B132" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C132" s="14" t="s">
+      <c r="C132" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="10"/>
-      <c r="B133" s="10"/>
-      <c r="C133" s="10"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="9" t="s">
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="A133" s="9"/>
+      <c r="B133" s="9"/>
+      <c r="C133" s="9"/>
+    </row>
+    <row r="134" ht="15.75" customHeight="1">
+      <c r="A134" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B134" s="10"/>
-      <c r="C134" s="10"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="10"/>
-      <c r="B135" s="10" t="s">
+      <c r="B134" s="9"/>
+      <c r="C134" s="9"/>
+    </row>
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="A135" s="9"/>
+      <c r="B135" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C135" s="10" t="s">
+      <c r="C135" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="10"/>
-      <c r="B136" s="10" t="s">
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="A136" s="9"/>
+      <c r="B136" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C136" s="10" t="s">
+      <c r="C136" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="10"/>
-      <c r="B137" s="10" t="s">
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="A137" s="9"/>
+      <c r="B137" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C137" s="11">
+      <c r="C137" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="10"/>
-      <c r="B138" s="10" t="s">
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="A138" s="9"/>
+      <c r="B138" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C138" s="10"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="10"/>
-      <c r="B139" s="10" t="s">
+      <c r="C138" s="9"/>
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="A139" s="9"/>
+      <c r="B139" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C139" s="9" t="s">
+      <c r="C139" s="8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="10"/>
-      <c r="B140" s="10" t="s">
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="A140" s="9"/>
+      <c r="B140" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C140" s="12" t="s">
+      <c r="C140" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="10"/>
-      <c r="B141" s="13" t="s">
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="A141" s="9"/>
+      <c r="B141" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C141" s="14" t="s">
+      <c r="C141" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="10"/>
-      <c r="B142" s="10"/>
-      <c r="C142" s="10"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="9" t="s">
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="A142" s="9"/>
+      <c r="B142" s="9"/>
+      <c r="C142" s="9"/>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B143" s="10"/>
-      <c r="C143" s="10"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="10"/>
-      <c r="B144" s="10" t="s">
+      <c r="B143" s="9"/>
+      <c r="C143" s="9"/>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="A144" s="9"/>
+      <c r="B144" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C144" s="10" t="s">
+      <c r="C144" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="10"/>
-      <c r="B145" s="10" t="s">
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="A145" s="9"/>
+      <c r="B145" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C145" s="10" t="s">
+      <c r="C145" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="10"/>
-      <c r="B146" s="10" t="s">
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="A146" s="9"/>
+      <c r="B146" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C146" s="11">
+      <c r="C146" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="10"/>
-      <c r="B147" s="10" t="s">
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="A147" s="9"/>
+      <c r="B147" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C147" s="10"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="10"/>
-      <c r="B148" s="10" t="s">
+      <c r="C147" s="9"/>
+    </row>
+    <row r="148" ht="15.75" customHeight="1">
+      <c r="A148" s="9"/>
+      <c r="B148" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C148" s="9" t="s">
+      <c r="C148" s="8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="10"/>
-      <c r="B149" s="10" t="s">
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="A149" s="9"/>
+      <c r="B149" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C149" s="12" t="s">
+      <c r="C149" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="10"/>
-      <c r="B150" s="13" t="s">
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="A150" s="9"/>
+      <c r="B150" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C150" s="14" t="s">
+      <c r="C150" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="10"/>
-      <c r="B151" s="10"/>
-      <c r="C151" s="10"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="9" t="s">
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="A151" s="9"/>
+      <c r="B151" s="9"/>
+      <c r="C151" s="9"/>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="A152" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B152" s="10"/>
-      <c r="C152" s="10"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="10"/>
-      <c r="B153" s="10" t="s">
+      <c r="B152" s="9"/>
+      <c r="C152" s="9"/>
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="A153" s="9"/>
+      <c r="B153" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C153" s="10" t="s">
+      <c r="C153" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="10"/>
-      <c r="B154" s="10" t="s">
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="A154" s="9"/>
+      <c r="B154" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C154" s="10" t="s">
+      <c r="C154" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="10"/>
-      <c r="B155" s="10" t="s">
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="A155" s="9"/>
+      <c r="B155" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C155" s="11">
+      <c r="C155" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="10"/>
-      <c r="B156" s="10" t="s">
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="A156" s="9"/>
+      <c r="B156" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C156" s="10"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="10"/>
-      <c r="B157" s="10" t="s">
+      <c r="C156" s="9"/>
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="A157" s="9"/>
+      <c r="B157" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C157" s="9" t="s">
+      <c r="C157" s="8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="10"/>
-      <c r="B158" s="10" t="s">
+    <row r="158" ht="15.75" customHeight="1">
+      <c r="A158" s="9"/>
+      <c r="B158" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C158" s="12" t="s">
+      <c r="C158" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="10"/>
-      <c r="B159" s="13" t="s">
+    <row r="159" ht="15.75" customHeight="1">
+      <c r="A159" s="9"/>
+      <c r="B159" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C159" s="14" t="s">
+      <c r="C159" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="10"/>
-      <c r="B160" s="10"/>
-      <c r="C160" s="10"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="9" t="s">
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="A160" s="9"/>
+      <c r="B160" s="9"/>
+      <c r="C160" s="9"/>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="A161" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B161" s="10"/>
-      <c r="C161" s="10"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="10"/>
-      <c r="B162" s="10" t="s">
+      <c r="B161" s="9"/>
+      <c r="C161" s="9"/>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="A162" s="9"/>
+      <c r="B162" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C162" s="10" t="s">
+      <c r="C162" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="10"/>
-      <c r="B163" s="10" t="s">
+    <row r="163" ht="15.75" customHeight="1">
+      <c r="A163" s="9"/>
+      <c r="B163" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C163" s="10" t="s">
+      <c r="C163" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="10"/>
-      <c r="B164" s="10" t="s">
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="A164" s="9"/>
+      <c r="B164" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C164" s="11">
+      <c r="C164" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="10"/>
-      <c r="B165" s="10" t="s">
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="A165" s="9"/>
+      <c r="B165" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C165" s="10"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="10"/>
-      <c r="B166" s="10" t="s">
+      <c r="C165" s="9"/>
+    </row>
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="A166" s="9"/>
+      <c r="B166" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C166" s="9" t="s">
+      <c r="C166" s="8" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="10"/>
-      <c r="B167" s="10" t="s">
+    <row r="167" ht="15.75" customHeight="1">
+      <c r="A167" s="9"/>
+      <c r="B167" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C167" s="12" t="s">
+      <c r="C167" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="10"/>
-      <c r="B168" s="13" t="s">
+    <row r="168" ht="15.75" customHeight="1">
+      <c r="A168" s="9"/>
+      <c r="B168" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C168" s="14" t="s">
+      <c r="C168" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="10"/>
-      <c r="B169" s="10"/>
-      <c r="C169" s="10"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="9" t="s">
+    <row r="169" ht="15.75" customHeight="1">
+      <c r="A169" s="9"/>
+      <c r="B169" s="9"/>
+      <c r="C169" s="9"/>
+    </row>
+    <row r="170" ht="15.75" customHeight="1">
+      <c r="A170" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B170" s="10"/>
-      <c r="C170" s="10"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="10"/>
-      <c r="B171" s="10" t="s">
+      <c r="B170" s="9"/>
+      <c r="C170" s="9"/>
+    </row>
+    <row r="171" ht="15.75" customHeight="1">
+      <c r="A171" s="9"/>
+      <c r="B171" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C171" s="10" t="s">
+      <c r="C171" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="10"/>
-      <c r="B172" s="10" t="s">
+    <row r="172" ht="15.75" customHeight="1">
+      <c r="A172" s="9"/>
+      <c r="B172" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C172" s="10" t="s">
+      <c r="C172" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="10"/>
-      <c r="B173" s="10" t="s">
+    <row r="173" ht="15.75" customHeight="1">
+      <c r="A173" s="9"/>
+      <c r="B173" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C173" s="11">
+      <c r="C173" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="10"/>
-      <c r="B174" s="10" t="s">
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="A174" s="9"/>
+      <c r="B174" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C174" s="10"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="10"/>
-      <c r="B175" s="10" t="s">
+      <c r="C174" s="9"/>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="A175" s="9"/>
+      <c r="B175" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C175" s="9" t="s">
+      <c r="C175" s="8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="10"/>
-      <c r="B176" s="10" t="s">
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="A176" s="9"/>
+      <c r="B176" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C176" s="12" t="s">
+      <c r="C176" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="10"/>
-      <c r="B177" s="13" t="s">
+    <row r="177" ht="15.75" customHeight="1">
+      <c r="A177" s="9"/>
+      <c r="B177" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C177" s="14" t="s">
+      <c r="C177" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="10"/>
-      <c r="B178" s="10"/>
-      <c r="C178" s="10"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="9" t="s">
+    <row r="178" ht="15.75" customHeight="1">
+      <c r="A178" s="9"/>
+      <c r="B178" s="9"/>
+      <c r="C178" s="9"/>
+    </row>
+    <row r="179" ht="15.75" customHeight="1">
+      <c r="A179" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B179" s="10"/>
-      <c r="C179" s="10"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="10"/>
-      <c r="B180" s="10" t="s">
+      <c r="B179" s="9"/>
+      <c r="C179" s="9"/>
+    </row>
+    <row r="180" ht="15.75" customHeight="1">
+      <c r="A180" s="9"/>
+      <c r="B180" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C180" s="10" t="s">
+      <c r="C180" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="10"/>
-      <c r="B181" s="10" t="s">
+    <row r="181" ht="15.75" customHeight="1">
+      <c r="A181" s="9"/>
+      <c r="B181" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C181" s="10" t="s">
+      <c r="C181" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="10"/>
-      <c r="B182" s="10" t="s">
+    <row r="182" ht="15.75" customHeight="1">
+      <c r="A182" s="9"/>
+      <c r="B182" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C182" s="11">
+      <c r="C182" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="10"/>
-      <c r="B183" s="10" t="s">
+    <row r="183" ht="15.75" customHeight="1">
+      <c r="A183" s="9"/>
+      <c r="B183" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C183" s="10"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="10"/>
-      <c r="B184" s="10" t="s">
+      <c r="C183" s="9"/>
+    </row>
+    <row r="184" ht="15.75" customHeight="1">
+      <c r="A184" s="9"/>
+      <c r="B184" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C184" s="9" t="s">
+      <c r="C184" s="8" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="10"/>
-      <c r="B185" s="10" t="s">
+    <row r="185" ht="15.75" customHeight="1">
+      <c r="A185" s="9"/>
+      <c r="B185" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C185" s="12" t="s">
+      <c r="C185" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="10"/>
-      <c r="B186" s="13" t="s">
+    <row r="186" ht="15.75" customHeight="1">
+      <c r="A186" s="9"/>
+      <c r="B186" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C186" s="14" t="s">
+      <c r="C186" s="13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="10"/>
-      <c r="B187" s="10"/>
-      <c r="C187" s="10"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="9" t="s">
+    <row r="187" ht="15.75" customHeight="1">
+      <c r="A187" s="9"/>
+      <c r="B187" s="9"/>
+      <c r="C187" s="9"/>
+    </row>
+    <row r="188" ht="15.75" customHeight="1">
+      <c r="A188" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B188" s="10"/>
-      <c r="C188" s="10"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="10"/>
-      <c r="B189" s="10" t="s">
+      <c r="B188" s="9"/>
+      <c r="C188" s="9"/>
+    </row>
+    <row r="189" ht="15.75" customHeight="1">
+      <c r="A189" s="9"/>
+      <c r="B189" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C189" s="10" t="s">
+      <c r="C189" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="10"/>
-      <c r="B190" s="10" t="s">
+    <row r="190" ht="15.75" customHeight="1">
+      <c r="A190" s="9"/>
+      <c r="B190" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C190" s="10" t="s">
+      <c r="C190" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="10"/>
-      <c r="B191" s="10" t="s">
+    <row r="191" ht="15.75" customHeight="1">
+      <c r="A191" s="9"/>
+      <c r="B191" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C191" s="11">
+      <c r="C191" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="10"/>
-      <c r="B192" s="10" t="s">
+    <row r="192" ht="15.75" customHeight="1">
+      <c r="A192" s="9"/>
+      <c r="B192" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C192" s="10"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="10"/>
-      <c r="B193" s="10" t="s">
+      <c r="C192" s="9"/>
+    </row>
+    <row r="193" ht="15.75" customHeight="1">
+      <c r="A193" s="9"/>
+      <c r="B193" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C193" s="9" t="s">
+      <c r="C193" s="8" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="10"/>
-      <c r="B194" s="10" t="s">
+    <row r="194" ht="15.75" customHeight="1">
+      <c r="A194" s="9"/>
+      <c r="B194" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C194" s="12" t="s">
+      <c r="C194" s="11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="10"/>
-      <c r="B195" s="13" t="s">
+    <row r="195" ht="15.75" customHeight="1">
+      <c r="A195" s="9"/>
+      <c r="B195" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C195" s="14" t="s">
+      <c r="C195" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="10"/>
-      <c r="B196" s="10"/>
-      <c r="C196" s="10"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="9" t="s">
+    <row r="196" ht="15.75" customHeight="1">
+      <c r="A196" s="9"/>
+      <c r="B196" s="9"/>
+      <c r="C196" s="9"/>
+    </row>
+    <row r="197" ht="15.75" customHeight="1">
+      <c r="A197" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B197" s="10"/>
-      <c r="C197" s="10"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="10"/>
-      <c r="B198" s="10" t="s">
+      <c r="B197" s="9"/>
+      <c r="C197" s="9"/>
+    </row>
+    <row r="198" ht="15.75" customHeight="1">
+      <c r="A198" s="9"/>
+      <c r="B198" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C198" s="10" t="s">
+      <c r="C198" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="10"/>
-      <c r="B199" s="10" t="s">
+    <row r="199" ht="15.75" customHeight="1">
+      <c r="A199" s="9"/>
+      <c r="B199" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C199" s="10" t="s">
+      <c r="C199" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="10"/>
-      <c r="B200" s="10" t="s">
+    <row r="200" ht="15.75" customHeight="1">
+      <c r="A200" s="9"/>
+      <c r="B200" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C200" s="11">
+      <c r="C200" s="10">
         <v>1.0</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="10"/>
-      <c r="B201" s="10" t="s">
+    <row r="201" ht="15.75" customHeight="1">
+      <c r="A201" s="9"/>
+      <c r="B201" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C201" s="10"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="10"/>
-      <c r="B202" s="10" t="s">
+      <c r="C201" s="9"/>
+    </row>
+    <row r="202" ht="15.75" customHeight="1">
+      <c r="A202" s="9"/>
+      <c r="B202" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C202" s="9" t="s">
+      <c r="C202" s="8" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="10"/>
-      <c r="B203" s="10" t="s">
+    <row r="203" ht="15.75" customHeight="1">
+      <c r="A203" s="9"/>
+      <c r="B203" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C203" s="12" t="s">
+      <c r="C203" s="11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="10"/>
-      <c r="B204" s="13" t="s">
+    <row r="204" ht="15.75" customHeight="1">
+      <c r="A204" s="9"/>
+      <c r="B204" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C204" s="14" t="s">
+      <c r="C204" s="13" t="s">
         <v>78</v>
       </c>
     </row>
